--- a/tools/反切上字與聲母對映表.xlsx
+++ b/tools/反切上字與聲母對映表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\Piau-Im\tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{663CAC30-D30A-4C54-8994-2628CE2793BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9BBE05A-5E6D-4F96-BCE9-FF156B0D5342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3105" yWindow="1500" windowWidth="31455" windowHeight="10890" xr2:uid="{5D06E5C6-5959-4DA0-BB2D-0D1C2D700418}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5D06E5C6-5959-4DA0-BB2D-0D1C2D700418}"/>
   </bookViews>
   <sheets>
     <sheet name="反切上字表" sheetId="1" r:id="rId1"/>
@@ -56,9 +56,6 @@
     <t>清濁</t>
   </si>
   <si>
-    <t>反切上字</t>
-  </si>
-  <si>
     <t>脣音</t>
   </si>
   <si>
@@ -438,6 +435,10 @@
   </si>
   <si>
     <t>如 而 汝 人 儒 耳 兒 仍</t>
+  </si>
+  <si>
+    <t>切語上字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -870,7 +871,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>6</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.5">
@@ -878,22 +879,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.5">
@@ -901,22 +902,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.5">
@@ -924,22 +925,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.5">
@@ -947,22 +948,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.5">
@@ -970,22 +971,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.5">
@@ -993,22 +994,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.5">
@@ -1016,22 +1017,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.5">
@@ -1039,22 +1040,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.5">
@@ -1062,22 +1063,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.5">
@@ -1085,22 +1086,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.5">
@@ -1108,22 +1109,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.5">
@@ -1131,22 +1132,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.5">
@@ -1154,22 +1155,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.5">
@@ -1177,22 +1178,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.5">
@@ -1200,22 +1201,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="F16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.5">
@@ -1223,22 +1224,22 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.5">
@@ -1246,22 +1247,22 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.5">
@@ -1269,22 +1270,22 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E19" s="1" t="s">
+      <c r="F19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.5">
@@ -1292,22 +1293,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E20" s="1" t="s">
+      <c r="F20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.5">
@@ -1315,22 +1316,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.5">
@@ -1338,22 +1339,22 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E22" s="1" t="s">
+      <c r="F22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.5">
@@ -1361,22 +1362,22 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C23" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E23" s="1" t="s">
+      <c r="F23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.5">
@@ -1384,22 +1385,22 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="D24" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.5">
@@ -1407,22 +1408,22 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.5">
@@ -1430,22 +1431,22 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.5">
@@ -1453,22 +1454,22 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.5">
@@ -1476,22 +1477,22 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.5">
@@ -1499,22 +1500,22 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="E29" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.5">
@@ -1522,22 +1523,22 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C30" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="F30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.5">
@@ -1545,22 +1546,22 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E31" s="1" t="s">
+      <c r="F31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.5">
@@ -1568,22 +1569,22 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C32" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="E32" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="F32" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.5">
@@ -1591,22 +1592,22 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="F33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G33" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.5">
@@ -1614,22 +1615,22 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C34" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E34" s="1" t="s">
+      <c r="F34" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.5">
@@ -1637,19 +1638,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C35" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="F35" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G35" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.5">
@@ -1657,22 +1658,22 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C36" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.5">
@@ -1680,22 +1681,22 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C37" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E37" s="1" t="s">
+      <c r="F37" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.5">
@@ -1703,22 +1704,22 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="D38" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.5">
@@ -1726,22 +1727,22 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="D39" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E39" s="1" t="s">
+      <c r="F39" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>133</v>
       </c>
     </row>
   </sheetData>
